--- a/AAII_Financials/Quarterly/TAK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TAK_QTR_FIN.xlsx
@@ -656,372 +656,398 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7505000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6883700</v>
+      </c>
+      <c r="F8" s="3">
         <v>7600700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>7519500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>7670600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>7034500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>7277200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>8208900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>7509300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>6947700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>7882900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>6983600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7321800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>7192700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7785500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>6394700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>6554400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5798600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>6191900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>6091100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>6979600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5461200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6133400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6145800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6839800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>6798700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>7828400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7388600</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2501900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2851000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2558500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2568200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2666200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2492700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2651500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2752300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2405400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2560800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2692100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2300300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2220900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2255800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2385400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1948700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1974000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2047600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1933200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1988500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1773300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1796900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1855500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1944700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2030800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2186500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2546900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2461600</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5003100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4032600</v>
+      </c>
+      <c r="F10" s="3">
         <v>5042200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>4951300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5004400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4541800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4625700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5456500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5103900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4386900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5190800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4683300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>5100800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>4936900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>5400100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4446000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4580400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3751000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>4258600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>4102600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>5206300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>3664300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>4277900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>4201100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>4809000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>4612200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>5281400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>4927000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,91 +1077,99 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1029800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1182100</v>
+      </c>
+      <c r="F12" s="3">
         <v>1117600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1091200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>997300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1442500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1082500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1225500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1047200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1286200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1329300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1231500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1125600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1210700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1239900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>983400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>967900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>953700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>882000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>948800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>900200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>803200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>861800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>920400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>911200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1227300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1117900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1034000</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1217,174 +1251,192 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3311300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-125600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>680400</v>
       </c>
-      <c r="F14" s="3">
-        <v>15900</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1385500</v>
-      </c>
       <c r="H14" s="3">
+        <v>-108100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1474400</v>
+      </c>
+      <c r="J14" s="3">
         <v>-464900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>540200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>150400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1222800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-247900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>980300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>54100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>290100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>105800</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>219500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>183900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>201700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>123100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>208700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>152600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>325000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>203900</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>266400</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>649200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>654000</v>
+      </c>
+      <c r="F15" s="3">
         <v>868400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>888000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>896500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>911700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>853400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>969200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>861800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>884700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>949100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>885900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>841000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>886500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>962600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>908300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>884800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>991200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>811300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>740600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>755800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>810300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>729100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>809000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>889300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>1112500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>946800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>942600</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1411,174 +1463,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6270700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6119200</v>
+      </c>
+      <c r="F17" s="3">
         <v>6776300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6369600</v>
       </c>
-      <c r="F17" s="3">
-        <v>6375400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6213000</v>
-      </c>
       <c r="H17" s="3">
+        <v>6499500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>6253700</v>
+      </c>
+      <c r="J17" s="3">
         <v>7199900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6510400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6324900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5916100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7386500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6333700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6101700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>6160000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6741900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5728400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5539900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5809400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5391600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5388700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5152700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4393900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5084200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5769500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5412800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>7346100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>7340900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6806800</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1234200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>764500</v>
+      </c>
+      <c r="F18" s="3">
         <v>824400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1149900</v>
       </c>
-      <c r="F18" s="3">
-        <v>1295200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>821500</v>
-      </c>
       <c r="H18" s="3">
+        <v>1171100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>780800</v>
+      </c>
+      <c r="J18" s="3">
         <v>77300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1698500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1184400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1031600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>496300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>650000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1220000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1032700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1043600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>666300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1014500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-10800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>800200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>702400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1826900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1067300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1049200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>376300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1426900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-547400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>487500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>581800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1608,219 +1674,233 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-61200</v>
+        <v>169800</v>
       </c>
       <c r="E20" s="3">
+        <v>-1192200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1252800</v>
+      </c>
+      <c r="G20" s="3">
         <v>-512700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>544000</v>
       </c>
-      <c r="G20" s="3">
-        <v>166100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>293100</v>
-      </c>
       <c r="I20" s="3">
+        <v>-314400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>470000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-227200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>210100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>273700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-57200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>48000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>84600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-282800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-254500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>33400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-348100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-304300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-259400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-188000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-139400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-244400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-413100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-315600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-481300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-261200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-390000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1754000</v>
+        <v>1713600</v>
       </c>
       <c r="E21" s="3">
+        <v>2610700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>440000</v>
+      </c>
+      <c r="G21" s="3">
         <v>2550600</v>
       </c>
-      <c r="F21" s="3">
-        <v>1647600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1567200</v>
-      </c>
       <c r="H21" s="3">
-        <v>637600</v>
+        <v>1523500</v>
       </c>
       <c r="I21" s="3">
+        <v>2006800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>460700</v>
+      </c>
+      <c r="K21" s="3">
         <v>2895000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1836000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1642700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1453400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1593100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2013000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1834600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2016600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1482600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2114700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>652200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1507800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1457100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2689600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1916200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1829200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1045500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2319100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>255200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>4215800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>3307100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>219600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>319600</v>
+      </c>
+      <c r="F22" s="3">
         <v>-593100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1088600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>202400</v>
       </c>
-      <c r="G22" s="3">
-        <v>-65800</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>285100</v>
+      </c>
+      <c r="J22" s="3">
         <v>-140200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>581100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>165400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>-378600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>472200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>532200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>184000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>-73700</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1857,174 +1937,192 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1001100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2861700</v>
+      </c>
+      <c r="F23" s="3">
         <v>853800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>190400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1044000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-716500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>168000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>833200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>849200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-314200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>434600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-642600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>933900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>360400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>760800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>411800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1047900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-358900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>496000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>443000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1638900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>927900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>804800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-36800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1111400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1028700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>226300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>191800</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>304300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-544700</v>
+      </c>
+      <c r="F24" s="3">
         <v>192200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>269600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>182600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-28100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>16400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>190300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>256800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-294400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-315700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-321400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>315600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>126200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-85200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>18000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>340000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-283300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>98700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>111400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>626600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-469800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>127200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-68600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>407500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-1042400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>518800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-425900</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2106,174 +2204,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>696800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2317000</v>
+      </c>
+      <c r="F26" s="3">
         <v>661600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-79300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>861400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-688500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>151600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>642900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>592400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-19800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>750200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-321200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>618400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>234200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>846000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>393900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>707800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-75500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>397200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>331600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1012300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1397800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>677600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>31700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>703900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>13800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-292500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>617700</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>696400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2317400</v>
+      </c>
+      <c r="F27" s="3">
         <v>661000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-79700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>861100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-688900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>151300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>642500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>592100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-20000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>750000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-321600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>618300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>234200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>845800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>393900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>707800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-75400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>396900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>331400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1012000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1397400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>677000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>31400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>703800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>15200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-293500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>617000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2355,8 +2471,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2438,8 +2560,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2521,8 +2649,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2604,174 +2738,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>61200</v>
+        <v>-169800</v>
       </c>
       <c r="E32" s="3">
+        <v>1192200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1252800</v>
+      </c>
+      <c r="G32" s="3">
         <v>512700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-544000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-166100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-293100</v>
-      </c>
       <c r="I32" s="3">
+        <v>314400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-470000</v>
+      </c>
+      <c r="K32" s="3">
         <v>227200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-210100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-273700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>57200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-48000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-84600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>282800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>254500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-33400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>348100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>304300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>259400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>188000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>139400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>244400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>413100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>315600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>481300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>261200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>390000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>696400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2317400</v>
+      </c>
+      <c r="F33" s="3">
         <v>661000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-79700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>861100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-688900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>151300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>642500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>592100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-20000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>750000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-321600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>618300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>234200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>845800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>393900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>707800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-75400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>396900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>331400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1012000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1397400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>677000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>31400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>703800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>15200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-293500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>617000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2853,179 +3005,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>696400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2317400</v>
+      </c>
+      <c r="F35" s="3">
         <v>661000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-79700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>861100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-688900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>151300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>642500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>592100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-20000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>750000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-321600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>618300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>234200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>845800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>393900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>707800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-75400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>396900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>331400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1012000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1397400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>677000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>31400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>703800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>15200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-293500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>617000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3055,8 +3225,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3086,91 +3258,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2836000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3742400</v>
+      </c>
+      <c r="F41" s="3">
         <v>4177200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4605000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2426000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2571700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3142900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5996000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4999600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3026700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2045700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2129400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2188200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4013500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4864500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>5092100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4354000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>5642000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4976200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4382800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4813700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6850500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>4527300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4914500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>5030900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>5617400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>5177000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4951400</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3211,630 +3391,678 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>294400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>203700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>125000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>168000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>189300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>185600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>220000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>259500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>268700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>119300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>95000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>139400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>183500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>126800</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5882300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5511400</v>
+      </c>
+      <c r="F43" s="3">
         <v>4834000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4745200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4709900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4843200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4675400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5033100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4801300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4612100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5271500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5276200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5709300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5128100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5537100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5107400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5352200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4809900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>5194500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>6397400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>6313300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5762100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>6076100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5996800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>6954300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>6915200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>7762900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>7340300</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8903700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>8783500</v>
+      </c>
+      <c r="F44" s="3">
         <v>8975100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>8781000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>8599300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>8129300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>7927900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>8421000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>7936700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>7998900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>8297600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>7738700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>7493000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>7420700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>6583700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>6083000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>6251400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>5665000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>5573800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>5648900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>5726700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>5345000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>5419500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>5791700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>6477500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>6692100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>7300200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>7660100</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1758800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1399200</v>
+      </c>
+      <c r="F45" s="3">
         <v>1890400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1604200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1683600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1292000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1772500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1867300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1579900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1278000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1615700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1339600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1706800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1476500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1151500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1030800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1101200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>936900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1089300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1095600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1128200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1017300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2888100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>3315900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2552100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>2391700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2536500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1552600</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19380900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19436500</v>
+      </c>
+      <c r="F46" s="3">
         <v>19876800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>19735400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>17418800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>16836200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>17518700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>21317400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19317500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16915700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17230400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>16483900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>17097300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>18038700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18431200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17517000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>17183700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>17221800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>17023100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>17710300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>18202000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>19234400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>19179700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>20138200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>21109700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>21755700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>22960200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>21631100</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>55300</v>
+      </c>
+      <c r="F47" s="3">
         <v>65000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>60300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>68900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>72100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>80700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>109100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>545100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>593900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>732900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>690300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>694500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>746000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2623200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2716400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2572000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2192100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2300200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>2538600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>2753700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>2469800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>2756500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>2723400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>2871500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>3254900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>3594200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>3193800</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13179600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13336900</v>
+      </c>
+      <c r="F48" s="3">
         <v>13291700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>13407300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13559200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>13143500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>12834100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>13175800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>12963500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>13155100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>13063800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>12681500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>12417000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>12722300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>11760600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>11230900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>11494200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>10509800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>10260900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>10526000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>10673500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>10308300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>9991800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>10648500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>11653500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>12213900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>13381200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>13273800</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>57079900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>58038200</v>
+      </c>
+      <c r="F49" s="3">
         <v>59117400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>58997100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>60428700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>59807100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>60260500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>62337600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>62784300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>64029300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>65324800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>64965900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>67062400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>68157000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>60042600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>58579200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>60381600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>54622600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>54684300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>56685400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>58177900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>56316000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>55572600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>60251000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>68474000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>72100100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>76638300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>77022400</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3916,8 +4144,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3999,91 +4233,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3343300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3251200</v>
+      </c>
+      <c r="F52" s="3">
         <v>3200400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2945800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2812200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2814100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3000100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2420000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2894300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2591600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2300700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2496800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2443200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2580300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3025800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3033400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3169400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2955800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2970300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3099300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3223500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>3219600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2556900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2949700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3487500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>3629300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2143100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2217000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4165,91 +4411,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>96362700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>97553600</v>
+      </c>
+      <c r="F54" s="3">
         <v>98277800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>97779600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>97067700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>95148800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>96087300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>101721300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>100877000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>99889500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>100899200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>99569400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>102311700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>104997600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>95883400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>93076800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>94801000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>87502000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>87238800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>90559600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>93030700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>91548200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>90057400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>96710900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>107596200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>112953800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>118716900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>117338100</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4279,8 +4537,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4310,506 +4570,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2748700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2982300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2966300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2920200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2059800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2927000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2885100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2914700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2115300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3431200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2819200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3049600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2312800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2705900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2479400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2860200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3428200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2412600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2426900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2356700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2437800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2396700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2124900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>2471500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2808800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2732000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2554500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3198900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3632600</v>
+      </c>
+      <c r="F58" s="3">
         <v>3719300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1985700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2572500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4096100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>861600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4356300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2727400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2865700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2626900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1840100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2883100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3003200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2641300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3625300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1900000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1354500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>844600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1549300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>178400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>157100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>2085200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2154800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>4953600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>5169900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>5572600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1561400</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11060300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>12138600</v>
+      </c>
+      <c r="F59" s="3">
         <v>9946200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>9506200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>9545100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>10582400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>9555500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>9421800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9682400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>10311700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>10131900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11192300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>11370200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>13354500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>10534100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>9154500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9845000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>9464900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>9172400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>9858000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>10009700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>9976900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>8748400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>9038500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>9903900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>11191000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>11075700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>10775600</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17007900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>17811200</v>
+      </c>
+      <c r="F60" s="3">
         <v>16647800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>14458200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15037700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>16738300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13344100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>16663200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>15324600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>15292700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>16190000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>15851500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>17302900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>18670500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>15881300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>15259200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>14605200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>14247600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>12429600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>13834200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>12544800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>12571800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>13230300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>13318300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>17329100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>19169700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>19380300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>14891500</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30862400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>30808800</v>
+      </c>
+      <c r="F61" s="3">
         <v>30862200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>33091800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>32368300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>29884900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>33684400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>34797900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>35176000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>33254600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>34307100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>33336700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>33376500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>33569100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>27795700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>26594500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>29119200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>27499000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>29073400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>28958800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>32204700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>32707700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>32740000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>36078700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>38335700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>39702200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>41997600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>44212800</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>950400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1129100</v>
+      </c>
+      <c r="F62" s="3">
         <v>853400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>842000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>857900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1068800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>723300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>672700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>624300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1547700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>639800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>604800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>947000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1959300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>8353200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>8391100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>8497400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>8016800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>9106200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>9378000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>9777100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>9562400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>10080000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>10961800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>11919100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>12432900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>12916700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>13870900</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4891,8 +5189,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4974,8 +5278,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5057,91 +5367,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>49859400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>50821400</v>
+      </c>
+      <c r="F66" s="3">
         <v>49523500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>49588900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>49477100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>48831100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>48897400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>53407700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>52394200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>51798500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>53066400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>52227900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>54439000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>57194400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>52034000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>50248400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>52225500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>49766800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>50612600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>52174000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>54529500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>54871300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>56080200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>60390800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>67618100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>71340000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>74332300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>73011400</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5171,8 +5493,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5254,8 +5578,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5337,8 +5667,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5420,8 +5756,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5503,91 +5845,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4103500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4480200</v>
+      </c>
+      <c r="F72" s="3">
         <v>6988200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>7761800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>8017200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7930600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>8211100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>9993300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>8318700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>9197700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>9909300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>9681300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>10306000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>11593300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>10704800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>9762700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>9838800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>9825300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>10077800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>11183800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>11053000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>10705200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>9577100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>10415700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>11345400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>12069500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>12557700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>13460800</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5669,8 +6023,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5752,8 +6112,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5835,91 +6201,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>46497200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>46724600</v>
+      </c>
+      <c r="F76" s="3">
         <v>48747000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>48184000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>47584200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>46311700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>47184000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>48307700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>48477700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>48086100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>47828000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>47337000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>47868400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>47799100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>43849400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>42828500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>42575400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>37735200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>36626200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>38385600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>38501200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>36676800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>33977100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>36320100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>39978100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>41613900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>44384600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>44326700</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6001,179 +6379,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>696400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2317400</v>
+      </c>
+      <c r="F81" s="3">
         <v>661000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-79700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>861100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-688900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>151300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>642500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>592100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-20000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>750000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-321600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>618300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>234200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>845800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>393900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>707800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-75400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>396900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>331400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1012000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1397400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>677000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>31400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>703800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>15200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-293500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>617000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6203,91 +6599,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>-1429500</v>
+        <v>294800</v>
       </c>
       <c r="E83" s="3">
+        <v>277700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>149100</v>
+      </c>
+      <c r="G83" s="3">
         <v>441600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>273000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>919500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1327000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>396200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>284300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>132400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>472700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>320700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>198700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>234600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1255800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1070700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1066800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1011100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1011800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1014100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1050700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>988300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1024400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1082400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1207700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1283900</v>
       </c>
-      <c r="AB83" s="3" t="s">
+      <c r="AD83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC83" s="3" t="s">
+      <c r="AE83" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6369,8 +6773,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6452,8 +6862,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6535,8 +6951,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6618,8 +7040,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6701,91 +7129,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>785200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>468700</v>
+      </c>
+      <c r="F89" s="3">
         <v>2380600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2555800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1493100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1483600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2440900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1961200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1058700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1841800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1038900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1331700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>639100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2209300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2685400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1409900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>567800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2493900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2387400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1681000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1226400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2843300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1598600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1915900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1244200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1633700</v>
       </c>
-      <c r="AB89" s="3" t="s">
+      <c r="AD89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC89" s="3" t="s">
+      <c r="AE89" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6815,91 +7255,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-331100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-291600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-265500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-270900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-332100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-325800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-286800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-345300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-357100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-294400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-334000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-253400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-317900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-269100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-50624000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-40609000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-98376000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-51823000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-48431000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-43491000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-219300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-256400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-180000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-213000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-197300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-328100</v>
       </c>
-      <c r="AB91" s="3" t="s">
+      <c r="AD91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC91" s="3" t="s">
+      <c r="AE91" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6981,8 +7429,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7064,91 +7518,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-539600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-364900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1465700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-325200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-230100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-131400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-735000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-524400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-974100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-406500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-534000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-405600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1843400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3298600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-331500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-173600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-638400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-170200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-475000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-237200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-517800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>2079700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>527600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>214700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>5600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>319300</v>
       </c>
-      <c r="AB94" s="3" t="s">
+      <c r="AD94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC94" s="3" t="s">
+      <c r="AE94" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7178,91 +7644,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>923600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>55300</v>
+      </c>
+      <c r="F96" s="3">
         <v>950500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>59400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1007100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>65000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>925100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>64200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>858500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>60300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>980800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>60700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>904300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>78400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-915800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-71000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-868600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-70700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-903100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-68800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-970400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-61500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-974300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-67300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-1135500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-73300</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7344,8 +7818,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7427,8 +7907,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7510,253 +7996,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1109500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-487400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1227400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-81000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1489500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2015300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-4172300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-768100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1966700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-384900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-693500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-941700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-399600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-49600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3088200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-331000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1453900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1618800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1154600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1783500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-3021100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-2623800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-2199500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1756200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1644300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AB100" s="3" t="s">
+      <c r="AD100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC100" s="3" t="s">
+      <c r="AE100" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-64800</v>
+      </c>
+      <c r="F101" s="3">
         <v>145500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-291700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>107000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>69800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-22100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>26800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>102100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-72600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>70700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>165500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>158200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>65300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>151500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>127500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>42200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>24400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>172300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-23700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-54400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-74100</v>
       </c>
-      <c r="AB101" s="3" t="s">
+      <c r="AD101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC101" s="3" t="s">
+      <c r="AE101" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-824800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-376600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-169300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2239900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-243300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-728000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2320900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>376900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2158400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1120200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-210600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1501900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1140500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-802300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>970700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1373000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>832400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>800100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-339200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-2288100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>2471500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-97000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>320000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-408000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>610800</v>
       </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AD102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AE102" s="3" t="s">
         <v>10</v>
       </c>
     </row>
